--- a/data/trans_dic/P57_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P57_R-Habitat-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,88; 22,13</t>
+          <t>15,65; 21,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,63; 18,98</t>
+          <t>13,36; 19,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,58; 27,21</t>
+          <t>20,83; 27,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 21,85</t>
+          <t>17,06; 21,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,07; 24,05</t>
+          <t>19,4; 23,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,16; 19,74</t>
+          <t>16,04; 19,56</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,72; 22,53</t>
+          <t>17,64; 22,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 12,82</t>
+          <t>4,63; 12,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,1; 26,73</t>
+          <t>21,31; 26,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,29; 19,11</t>
+          <t>15,3; 19,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,13; 23,94</t>
+          <t>20,23; 23,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 14,99</t>
+          <t>8,15; 15,1</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,72; 20,51</t>
+          <t>14,59; 20,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 11,54</t>
+          <t>6,92; 11,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,77; 22,73</t>
+          <t>16,59; 22,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 10,34</t>
+          <t>3,76; 10,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,51; 20,54</t>
+          <t>16,44; 20,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 10,16</t>
+          <t>5,1; 9,85</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,08; 20,06</t>
+          <t>15,22; 20,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,01; 18,81</t>
+          <t>13,96; 18,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,83; 28,62</t>
+          <t>22,67; 28,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,7; 22,11</t>
+          <t>15,57; 21,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,07; 23,75</t>
+          <t>19,79; 23,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,84; 19,71</t>
+          <t>15,91; 19,68</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,16; 19,78</t>
+          <t>17,26; 19,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,88</t>
+          <t>9,62; 13,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,11; 25,03</t>
+          <t>21,94; 24,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,85; 17,37</t>
+          <t>12,66; 17,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,07; 22,14</t>
+          <t>20,09; 22,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,3; 15,33</t>
+          <t>12,52; 15,33</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>106306; 148148</t>
+          <t>104768; 147247</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85708; 119313</t>
+          <t>83971; 120246</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>137347; 181629</t>
+          <t>139034; 183459</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115388; 146435</t>
+          <t>114335; 144793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>254922; 321567</t>
+          <t>259422; 317738</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>209942; 256360</t>
+          <t>208274; 254031</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>180937; 230121</t>
+          <t>180112; 231454</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60488; 152794</t>
+          <t>55219; 152915</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>219883; 278460</t>
+          <t>222043; 279381</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>145263; 181504</t>
+          <t>145304; 182315</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>415347; 493977</t>
+          <t>417421; 492102</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>181872; 320962</t>
+          <t>174612; 323283</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>111369; 155181</t>
+          <t>110366; 153406</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47118; 81305</t>
+          <t>48741; 80547</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>130705; 177105</t>
+          <t>129265; 173984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31758; 96077</t>
+          <t>34993; 93511</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>253622; 315437</t>
+          <t>252525; 317644</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83852; 165977</t>
+          <t>83345; 161039</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>140782; 187229</t>
+          <t>142035; 189120</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>129601; 173985</t>
+          <t>129061; 172269</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>237290; 297506</t>
+          <t>235606; 296078</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>171277; 241146</t>
+          <t>169818; 238123</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>395965; 468633</t>
+          <t>390532; 468008</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>319367; 397310</t>
+          <t>320609; 396770</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>580009; 668542</t>
+          <t>583378; 673888</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>337766; 478937</t>
+          <t>331725; 479683</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>780032; 882980</t>
+          <t>774090; 877276</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>467756; 632423</t>
+          <t>460815; 630378</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1386274; 1529294</t>
+          <t>1388120; 1525323</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>872095; 1086800</t>
+          <t>887320; 1086718</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P57_R-Habitat-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,65; 21,99</t>
+          <t>16,19; 22,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,36; 19,13</t>
+          <t>13,34; 18,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,83; 27,49</t>
+          <t>20,87; 27,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,06; 21,6</t>
+          <t>17,11; 21,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,4; 23,77</t>
+          <t>19,22; 23,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,04; 19,56</t>
+          <t>16,04; 19,35</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,64; 22,66</t>
+          <t>17,69; 22,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 12,83</t>
+          <t>10,35; 14,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,31; 26,81</t>
+          <t>21,08; 26,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,3; 19,2</t>
+          <t>15,43; 19,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,23; 23,85</t>
+          <t>20,11; 23,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 15,1</t>
+          <t>13,38; 16,25</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,59; 20,28</t>
+          <t>14,7; 20,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 11,43</t>
+          <t>7,2; 11,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,59; 22,33</t>
+          <t>16,67; 22,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 10,06</t>
+          <t>8,31; 12,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,44; 20,68</t>
+          <t>16,34; 20,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,85</t>
+          <t>8,28; 11,14</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,22; 20,26</t>
+          <t>15,3; 19,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,96; 18,63</t>
+          <t>14,42; 19,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,67; 28,48</t>
+          <t>22,88; 28,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,57; 21,83</t>
+          <t>18,93; 23,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,79; 23,72</t>
+          <t>19,94; 23,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,91; 19,68</t>
+          <t>17,37; 20,46</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -952,22 +952,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,26; 19,93</t>
+          <t>17,29; 20,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,62; 13,91</t>
+          <t>12,23; 14,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,94; 24,87</t>
+          <t>22,03; 24,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,66; 17,32</t>
+          <t>16,15; 18,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,52; 15,33</t>
+          <t>14,67; 16,23</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>102552</t>
+          <t>108359</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129235</t>
+          <t>140409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>231787</t>
+          <t>248768</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>104768; 147247</t>
+          <t>108387; 148968</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83971; 120246</t>
+          <t>91185; 127834</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>139034; 183459</t>
+          <t>139259; 184211</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114335; 144793</t>
+          <t>124383; 158246</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>259422; 317738</t>
+          <t>257015; 313325</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>208274; 254031</t>
+          <t>226223; 272858</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>114896</t>
+          <t>126606</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>162421</t>
+          <t>184323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>277317</t>
+          <t>310929</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>180112; 231454</t>
+          <t>180715; 232074</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55219; 152915</t>
+          <t>108422; 151473</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>222043; 279381</t>
+          <t>219670; 278249</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>145304; 182315</t>
+          <t>164061; 204705</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>417421; 492102</t>
+          <t>414835; 491302</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>174612; 323283</t>
+          <t>282312; 343059</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62693</t>
+          <t>72473</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69111</t>
+          <t>82627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>131805</t>
+          <t>155100</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>110366; 153406</t>
+          <t>111224; 152983</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48741; 80547</t>
+          <t>57833; 92060</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>129265; 173984</t>
+          <t>129919; 174856</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34993; 93511</t>
+          <t>67171; 98825</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>252525; 317644</t>
+          <t>250888; 317640</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83345; 161039</t>
+          <t>133385; 179437</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>149735</t>
+          <t>164368</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213083</t>
+          <t>234599</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>362817</t>
+          <t>398967</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>142035; 189120</t>
+          <t>142791; 186262</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>129061; 172269</t>
+          <t>142442; 188468</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>235606; 296078</t>
+          <t>237805; 298556</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>169818; 238123</t>
+          <t>210997; 258353</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>390532; 468008</t>
+          <t>393325; 468370</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>320609; 396770</t>
+          <t>365342; 430229</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>429876</t>
+          <t>471807</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>573850</t>
+          <t>641958</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1003726</t>
+          <t>1113764</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>583378; 673888</t>
+          <t>584516; 679576</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>331725; 479683</t>
+          <t>430826; 514378</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>774090; 877276</t>
+          <t>777164; 880662</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>460815; 630378</t>
+          <t>599754; 677803</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1388120; 1525323</t>
+          <t>1388057; 1525720</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>887320; 1086718</t>
+          <t>1061579; 1174508</t>
         </is>
       </c>
     </row>
